--- a/zawodnicy_id.xlsx
+++ b/zawodnicy_id.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,287 +487,270 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mitchell</t>
+          <t>Usman</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Baker</t>
+          <t>Diarra</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[Stany Zjednaczone] Georgetown Hoyas (Georgetown University)</t>
+          <t>[Bangladesz] Dhaka Wanderers</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Usman</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Diarra</t>
+          <t>Diks</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[Bangladesz] Dhaka Wanderers</t>
+          <t>[Niemcy] Borussia Mönchengladbach</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Mees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Diks</t>
+          <t>Hilgers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[Niemcy] Borussia Mönchengladbach</t>
+          <t>[Holandia] SC Heerenveen</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mees</t>
+          <t>Justin</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hilgers</t>
+          <t>Hubner</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[Holandia] SC Heerenveen</t>
+          <t>[Holandia] Fortuna Sittard</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Justin</t>
+          <t>Jay</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hubner</t>
+          <t>Idzes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[Holandia] Fortuna Sittard</t>
+          <t>[Włochy] US Sassuolo</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jay</t>
+          <t>Dean</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Idzes</t>
+          <t>James</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[Włochy] US Sassuolo</t>
+          <t>[Holandia] Go Ahead Eagles Deventer</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dean</t>
+          <t>Miliano</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Jonathans</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[Holandia] Go Ahead Eagles Deventer</t>
+          <t>[Holandia] FC Utrecht</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Miliano</t>
+          <t>Asnawi</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jonathans</t>
+          <t>Mangkualam</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[Holandia] FC Utrecht</t>
+          <t>[Tajlandia] Port FC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Asnawi</t>
+          <t>Maarten</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mangkualam</t>
+          <t>Paes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[Tajlandia] Port FC</t>
+          <t>[Holandia] Ajax Amsterdam</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Maarten</t>
+          <t>Joey</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Paes</t>
+          <t>Pelupessy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[Holandia] Ajax Amsterdam</t>
+          <t>[Belgia] Lommel SK</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Joey</t>
+          <t>Ole</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pelupessy</t>
+          <t>Romeny</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[Belgia] Lommel SK</t>
+          <t>[Holandia] Fortuna Sittard</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ole</t>
+          <t>Nathan</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Romeny</t>
+          <t>Tjoe-A-On</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[Holandia] Fortuna Sittard</t>
+          <t>[Holandia] Willem II Tilburg</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nathan</t>
+          <t>Muhammad</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tjoe-A-On</t>
+          <t>Toha</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[Holandia] Willem II Tilburg</t>
+          <t>[Brunei Darussalam] Brunei DPMM FC</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Muhammad</t>
+          <t>Calvin</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Toha</t>
+          <t>Verdonk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[Brunei Darussalam] Brunei DPMM FC</t>
+          <t>[Francja] LOSC Lille</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Calvin</t>
+          <t>Luke</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Verdonk</t>
+          <t>Vickery</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[Francja] LOSC Lille</t>
+          <t>[Australia] Macarthur FC</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Luke</t>
+          <t>Adrian</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vickery</t>
+          <t>Wibowo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
-        <is>
-          <t>[Australia] Macarthur FC</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Adrian</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Wibowo</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
         <is>
           <t>[Austria] FC Wacker Innsbruck</t>
         </is>
